--- a/ci-cd-merge-resolver/repoCollector/datasets/yudao-cloud.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/yudao-cloud.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="285">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -44,6 +44,78 @@
     <t>isMultiModule</t>
   </si>
   <si>
+    <t>dd30e9e111652efed45b98d8905e28c21d706eed</t>
+  </si>
+  <si>
+    <t>c5fbd548a84e16da5df44affbd0b93fcff11615b</t>
+  </si>
+  <si>
+    <t>96c6f184fadf8387ba0e654095d633786aaa3f4f</t>
+  </si>
+  <si>
+    <t>e07a81f81c2e785bc921e2404f844e9cdd42fb10</t>
+  </si>
+  <si>
+    <t>cbba929db8f8480443f449535808fae43d265052</t>
+  </si>
+  <si>
+    <t>edb5cdd372dca0c35aad24e5583f12556c79ae54</t>
+  </si>
+  <si>
+    <t>d5ed2f47280bdeec46affd99ba20290d2a29131b</t>
+  </si>
+  <si>
+    <t>51da2a2f367b8ce7a3993d70a03732b6d42505c0</t>
+  </si>
+  <si>
+    <t>9defcf736c37967dc1bf653c30b6d94f66101020</t>
+  </si>
+  <si>
+    <t>c6f8680da38571c77dd78664a9187fe9ee43a0a8</t>
+  </si>
+  <si>
+    <t>efae658cc5e6ee9e8bf8ba4b6a2397eb5a9a2264</t>
+  </si>
+  <si>
+    <t>f6eff0505390617c81bf1c54dda6be7ac9650b01</t>
+  </si>
+  <si>
+    <t>1b2abcc10ebd513db5f335b603e943327f4c3a61</t>
+  </si>
+  <si>
+    <t>ad5f07ce02351619c0132330e16890b5a8f39385</t>
+  </si>
+  <si>
+    <t>045b362142dfa580ba17462237f1228045648191</t>
+  </si>
+  <si>
+    <t>921398e437bfb37e4f4a4dd0279e61ec78974409</t>
+  </si>
+  <si>
+    <t>2cabcbcf8daf0f048401ab984b1099e70a91cde4</t>
+  </si>
+  <si>
+    <t>816e1fbf9ba8eababd78a48786078fee9e0e4e44</t>
+  </si>
+  <si>
+    <t>e10be5160b40beeded5334dfb0c9fa47de4a4785</t>
+  </si>
+  <si>
+    <t>61b6b6c7bd325826a4ab9f43493340f3e3888ca4</t>
+  </si>
+  <si>
+    <t>17a1af1069de3b219aac611ae95a268d778d69a4</t>
+  </si>
+  <si>
+    <t>7739c2a35df810f80a89bfbe7b59654eead2c0e9</t>
+  </si>
+  <si>
+    <t>cad6da432ba539747e8bc343dece9580f118a473</t>
+  </si>
+  <si>
+    <t>0f27c0aa72a5910188dba352044fd9323205170b</t>
+  </si>
+  <si>
     <t>88c9335f7aea833e3904f8eaa4c8bbaf29b73e5d</t>
   </si>
   <si>
@@ -53,13 +125,49 @@
     <t>adadcf4f6264f746ede016f560fcb8dcae5dbe87</t>
   </si>
   <si>
-    <t>dd30e9e111652efed45b98d8905e28c21d706eed</t>
-  </si>
-  <si>
-    <t>c5fbd548a84e16da5df44affbd0b93fcff11615b</t>
-  </si>
-  <si>
-    <t>96c6f184fadf8387ba0e654095d633786aaa3f4f</t>
+    <t>4f1de29748194964c31a0c5e3128b3453042ff5c</t>
+  </si>
+  <si>
+    <t>2a6b685ed710f3cc27192f5ad6360cde929b5522</t>
+  </si>
+  <si>
+    <t>3c1748aff13402e069ce24d73da17d4e05d7d9ea</t>
+  </si>
+  <si>
+    <t>78dea8a9cc6c273c3c017334ff1467ad00961889</t>
+  </si>
+  <si>
+    <t>b584e56023f9e6ab0abbada43050670078fdb9c5</t>
+  </si>
+  <si>
+    <t>44c9391254406be85231d3f688f10a07bd43b9a2</t>
+  </si>
+  <si>
+    <t>0b06e29877dc9aceb9b3f0d2106f9fb20e174b07</t>
+  </si>
+  <si>
+    <t>14cfabfb9a9a5bf9422409124ab1bf6a0ec130ec</t>
+  </si>
+  <si>
+    <t>949ef86bbf1a7f891302f1c443a571cbded49d70</t>
+  </si>
+  <si>
+    <t>d369c8210cb2d08890047a850accb1e620e26f63</t>
+  </si>
+  <si>
+    <t>6c295f87827775fe617ce2380c77d0a68f410dd8</t>
+  </si>
+  <si>
+    <t>a1f7f81e8d9eb07ab12f53cc7e57470c23cf6fac</t>
+  </si>
+  <si>
+    <t>382e9e8cdd2c53bc33544eb7b4ea6440abc493a5</t>
+  </si>
+  <si>
+    <t>4017f71d10488463b8f2ce255b9ef83bd0ee8a34</t>
+  </si>
+  <si>
+    <t>8e07be59d5c02edd2aafda07067e1d24e2334a27</t>
   </si>
   <si>
     <t>104d94977b5ea79e5cab1a8956a882483669c356</t>
@@ -71,13 +179,40 @@
     <t>a277987139b55e5cabce96bf8ef73cb45299e507</t>
   </si>
   <si>
-    <t>921398e437bfb37e4f4a4dd0279e61ec78974409</t>
-  </si>
-  <si>
-    <t>2cabcbcf8daf0f048401ab984b1099e70a91cde4</t>
-  </si>
-  <si>
-    <t>816e1fbf9ba8eababd78a48786078fee9e0e4e44</t>
+    <t>b8aa12595550fb5c65b298bca3ad0b5fe697b548</t>
+  </si>
+  <si>
+    <t>a552b5a814dc3841b6c85db22e5325eeaee90335</t>
+  </si>
+  <si>
+    <t>cc2aa364d558868d1d40e31999b94aad7e4506c8</t>
+  </si>
+  <si>
+    <t>c015b68db87e5d3a8cc56eed805cb80928c34a09</t>
+  </si>
+  <si>
+    <t>2321829cc326287c1d16c7c2d2320566a4c39219</t>
+  </si>
+  <si>
+    <t>24402eaeef5b921d63febaf21127922582c95aa5</t>
+  </si>
+  <si>
+    <t>273d8f6a2a49dd071a70058ee5bea0ed592a6393</t>
+  </si>
+  <si>
+    <t>9252e7b5f02cfc6ff63f1bac91bbdc2d90434970</t>
+  </si>
+  <si>
+    <t>e792054adb260ddda3d4086014d1815783fb6e18</t>
+  </si>
+  <si>
+    <t>6980b8cab93826f9ed95ed2d40db3babe2068156</t>
+  </si>
+  <si>
+    <t>41ef63d5d0665428b088973efcbf524ca04fae91</t>
+  </si>
+  <si>
+    <t>178ee2004b77c19f221f0c21e6cb7c79380f00e0</t>
   </si>
   <si>
     <t>7b6c81beaa42cacad4216549330020e873c09355</t>
@@ -89,6 +224,15 @@
     <t>c854fda3f1f2f262cea9f200e38732fb2d6110fa</t>
   </si>
   <si>
+    <t>829d20030294c2b410d2bde1abefd6e00544b9cb</t>
+  </si>
+  <si>
+    <t>0d51d6c8b64290917457466f2a793bbe3ff49d02</t>
+  </si>
+  <si>
+    <t>fdbda9598462fad232b609a35091a73843706cf7</t>
+  </si>
+  <si>
     <t>ec990c9a4fe465e51b4f5efba45ccd6be1ebc37b</t>
   </si>
   <si>
@@ -98,39 +242,48 @@
     <t>9f8188dcd41621cca3879f27490dbdb60883d6b4</t>
   </si>
   <si>
-    <t>829d20030294c2b410d2bde1abefd6e00544b9cb</t>
-  </si>
-  <si>
-    <t>0d51d6c8b64290917457466f2a793bbe3ff49d02</t>
-  </si>
-  <si>
-    <t>fdbda9598462fad232b609a35091a73843706cf7</t>
-  </si>
-  <si>
-    <t>e07a81f81c2e785bc921e2404f844e9cdd42fb10</t>
-  </si>
-  <si>
-    <t>cbba929db8f8480443f449535808fae43d265052</t>
-  </si>
-  <si>
-    <t>edb5cdd372dca0c35aad24e5583f12556c79ae54</t>
-  </si>
-  <si>
-    <t>1b2abcc10ebd513db5f335b603e943327f4c3a61</t>
-  </si>
-  <si>
-    <t>ad5f07ce02351619c0132330e16890b5a8f39385</t>
-  </si>
-  <si>
-    <t>045b362142dfa580ba17462237f1228045648191</t>
-  </si>
-  <si>
     <t>3efadfebe589dcaf6b50fd3386fa1196377dcefb</t>
   </si>
   <si>
     <t>c10d96d0c784eea112529381decceb342fda31a5</t>
   </si>
   <si>
+    <t>91614e9898f6e3cb35b6eed539c5e96996c9b0b1</t>
+  </si>
+  <si>
+    <t>603a0ffb836eabe40e9f14b4c80f0740f06aee9e</t>
+  </si>
+  <si>
+    <t>08c31e889d5bd2fc32bb66ef79bd638920fdd901</t>
+  </si>
+  <si>
+    <t>2084321637a3cd8ba7e851e39699da608a02a1f0</t>
+  </si>
+  <si>
+    <t>a31ff349f61a4e7198538880b79015d14e8f2e6e</t>
+  </si>
+  <si>
+    <t>f92f9d2e1733f257dcf3fbe155b34079cba0d211</t>
+  </si>
+  <si>
+    <t>e909c1bdf69a888eaead2f9d61cfded5ff1ba9f5</t>
+  </si>
+  <si>
+    <t>a2740634be06ffb3c1df952f0104cda26a11a271</t>
+  </si>
+  <si>
+    <t>b46f29e45f758148b0c7653998879f3a353e24a7</t>
+  </si>
+  <si>
+    <t>db28fd38cd27ae74c616da2066147e2e6b4165a8</t>
+  </si>
+  <si>
+    <t>c2cf376c0dd69331d8fbbfa42f9de8dfcdfbafde</t>
+  </si>
+  <si>
+    <t>6161166af95a9ab302a26e4916fe0e30acdd87ec</t>
+  </si>
+  <si>
     <t>393d7b728c22e6da48dfb5d8d97431214ddf8e9c</t>
   </si>
   <si>
@@ -140,40 +293,10 @@
     <t>8c7331873e9d9563480486c72a6e73a29d6fd184</t>
   </si>
   <si>
-    <t>78dea8a9cc6c273c3c017334ff1467ad00961889</t>
-  </si>
-  <si>
-    <t>b584e56023f9e6ab0abbada43050670078fdb9c5</t>
-  </si>
-  <si>
-    <t>44c9391254406be85231d3f688f10a07bd43b9a2</t>
-  </si>
-  <si>
-    <t>0b06e29877dc9aceb9b3f0d2106f9fb20e174b07</t>
-  </si>
-  <si>
-    <t>14cfabfb9a9a5bf9422409124ab1bf6a0ec130ec</t>
-  </si>
-  <si>
-    <t>949ef86bbf1a7f891302f1c443a571cbded49d70</t>
-  </si>
-  <si>
-    <t>b8aa12595550fb5c65b298bca3ad0b5fe697b548</t>
-  </si>
-  <si>
-    <t>a552b5a814dc3841b6c85db22e5325eeaee90335</t>
-  </si>
-  <si>
-    <t>cc2aa364d558868d1d40e31999b94aad7e4506c8</t>
-  </si>
-  <si>
-    <t>273d8f6a2a49dd071a70058ee5bea0ed592a6393</t>
-  </si>
-  <si>
-    <t>9252e7b5f02cfc6ff63f1bac91bbdc2d90434970</t>
-  </si>
-  <si>
-    <t>e792054adb260ddda3d4086014d1815783fb6e18</t>
+    <t>7cca8d09b154546d6acfc7329c168a1de2103a26</t>
+  </si>
+  <si>
+    <t>953a33b4f7a62b7d33cca2374eb4cd82759620e0</t>
   </si>
   <si>
     <t>02ddf5a5a70ac430a347607d403ee928a509e0bc</t>
@@ -185,22 +308,22 @@
     <t>7d9de01556575af2b41b886f0935b7ffebcfe487</t>
   </si>
   <si>
-    <t>2084321637a3cd8ba7e851e39699da608a02a1f0</t>
-  </si>
-  <si>
-    <t>a31ff349f61a4e7198538880b79015d14e8f2e6e</t>
-  </si>
-  <si>
-    <t>f92f9d2e1733f257dcf3fbe155b34079cba0d211</t>
-  </si>
-  <si>
-    <t>91614e9898f6e3cb35b6eed539c5e96996c9b0b1</t>
-  </si>
-  <si>
-    <t>603a0ffb836eabe40e9f14b4c80f0740f06aee9e</t>
-  </si>
-  <si>
-    <t>08c31e889d5bd2fc32bb66ef79bd638920fdd901</t>
+    <t>d883e08fdd0ea68ee37ae6120175a7998a0026c4</t>
+  </si>
+  <si>
+    <t>85b75b9c1c8dfd92c38793c78873b663550e6dcd</t>
+  </si>
+  <si>
+    <t>7a0d5bd29a6c8f31828335649c3693aa546831cc</t>
+  </si>
+  <si>
+    <t>323396492e5ae1e2f0eeaedebddd42a7e9a87aaa</t>
+  </si>
+  <si>
+    <t>1d1ee4698e402bb10e00b4039fbbcb458f103006</t>
+  </si>
+  <si>
+    <t>aeb4136e9fe8f8bb956e08acd743d89049623cc8</t>
   </si>
   <si>
     <t>1e0c4503aa7a89827b604cd9d9efc5da2f963a2d</t>
@@ -212,19 +335,13 @@
     <t>d238b24471fcd60cf45a692b907b8f756c5f73d8</t>
   </si>
   <si>
-    <t>d883e08fdd0ea68ee37ae6120175a7998a0026c4</t>
-  </si>
-  <si>
-    <t>85b75b9c1c8dfd92c38793c78873b663550e6dcd</t>
-  </si>
-  <si>
-    <t>7a0d5bd29a6c8f31828335649c3693aa546831cc</t>
-  </si>
-  <si>
-    <t>7cca8d09b154546d6acfc7329c168a1de2103a26</t>
-  </si>
-  <si>
-    <t>953a33b4f7a62b7d33cca2374eb4cd82759620e0</t>
+    <t>58c8a7dbc2af4112579abf00b21d060b43018e72</t>
+  </si>
+  <si>
+    <t>0fa162876f9045456a2d3f326fccd28b070ab72b</t>
+  </si>
+  <si>
+    <t>5b816120860fa13ee7e0e4515d605cf1f015ffbf</t>
   </si>
   <si>
     <t>580f0abe641c6325ba63a36238a8b5ca230e8961</t>
@@ -236,24 +353,6 @@
     <t>d338b8687d2b1630c0d691f4c54fe7efceed0d7a</t>
   </si>
   <si>
-    <t>d369c8210cb2d08890047a850accb1e620e26f63</t>
-  </si>
-  <si>
-    <t>6c295f87827775fe617ce2380c77d0a68f410dd8</t>
-  </si>
-  <si>
-    <t>a1f7f81e8d9eb07ab12f53cc7e57470c23cf6fac</t>
-  </si>
-  <si>
-    <t>4f1de29748194964c31a0c5e3128b3453042ff5c</t>
-  </si>
-  <si>
-    <t>2a6b685ed710f3cc27192f5ad6360cde929b5522</t>
-  </si>
-  <si>
-    <t>3c1748aff13402e069ce24d73da17d4e05d7d9ea</t>
-  </si>
-  <si>
     <t>4e53fde33a30f73ddb486f628c25d9d88f9e5a59</t>
   </si>
   <si>
@@ -263,13 +362,76 @@
     <t>e005e4d9c68ff45de4f90a156d59aa04f0006589</t>
   </si>
   <si>
-    <t>e909c1bdf69a888eaead2f9d61cfded5ff1ba9f5</t>
-  </si>
-  <si>
-    <t>a2740634be06ffb3c1df952f0104cda26a11a271</t>
-  </si>
-  <si>
-    <t>b46f29e45f758148b0c7653998879f3a353e24a7</t>
+    <t>5a2668a5e5b42e3fd7132c3566a8717795ce09f8</t>
+  </si>
+  <si>
+    <t>e354108f31b1ae1c6a3cec2b432ca03f16ed108e</t>
+  </si>
+  <si>
+    <t>a7e38d8e34804323ae2f83f7729cbb0a0d56fba4</t>
+  </si>
+  <si>
+    <t>e392888032c3a56a721c569a0c6862bc25a1f2cf</t>
+  </si>
+  <si>
+    <t>eaa4ab7fa128048926b61d1f70f0d49363034a20</t>
+  </si>
+  <si>
+    <t>10c520bf000dab04c83fb82f31c0fc772f02bd20</t>
+  </si>
+  <si>
+    <t>d4f1971acdb5a4f991d13fe947d7cb64946dc9aa</t>
+  </si>
+  <si>
+    <t>a1fbbe35faa63a9f1a1ca987f620a5af0487cf3d</t>
+  </si>
+  <si>
+    <t>d796af204093535d862d91cdc694312dfbfbab5e</t>
+  </si>
+  <si>
+    <t>6b53d3bbd8baed16ee9c0c6620a2ba0446ed3804</t>
+  </si>
+  <si>
+    <t>c18760b9f42ae36f9268bbbb69368dd875eb62f5</t>
+  </si>
+  <si>
+    <t>ef82f01242447e4be903a243f40df566cdf28157</t>
+  </si>
+  <si>
+    <t>728e20ff230d675779e3bb40aa72f1742adbdbc7</t>
+  </si>
+  <si>
+    <t>a65f1dae9bf45dbc2e38eb504a0e476107046cd3</t>
+  </si>
+  <si>
+    <t>984145045883d730095faeeff1e1516b19b1082a</t>
+  </si>
+  <si>
+    <t>8dd21005d526da50a06efe1b94b5e6652187e141</t>
+  </si>
+  <si>
+    <t>b70c0908b4f7810a8c4cc855ffdc7e49af0806c2</t>
+  </si>
+  <si>
+    <t>f02685a11cf475251834fb29337a1ef60ee9468e</t>
+  </si>
+  <si>
+    <t>da6cea16ec2de89e83d1ff06dd56c089c556f4c3</t>
+  </si>
+  <si>
+    <t>ace340169396e29032a9450115679384a945e96c</t>
+  </si>
+  <si>
+    <t>76af487fd0630d89704285e0aad94fa36e704ca6</t>
+  </si>
+  <si>
+    <t>cec3bfe4bef1e53e0456fe8ae66f3b711f2f11d1</t>
+  </si>
+  <si>
+    <t>e203c9b2f0fa427ac06841038e228f68233a74a8</t>
+  </si>
+  <si>
+    <t>b4c0652dfa00e68ddd9ee7aecefc4207df8f9d67</t>
   </si>
   <si>
     <t>5912d91abedadd3688c9b5d82aa702e41984b4f4</t>
@@ -281,31 +443,46 @@
     <t>dfe018b8ce25cfa732a85a9875237c83b2448952</t>
   </si>
   <si>
-    <t>323396492e5ae1e2f0eeaedebddd42a7e9a87aaa</t>
-  </si>
-  <si>
-    <t>1d1ee4698e402bb10e00b4039fbbcb458f103006</t>
-  </si>
-  <si>
-    <t>aeb4136e9fe8f8bb956e08acd743d89049623cc8</t>
-  </si>
-  <si>
-    <t>6980b8cab93826f9ed95ed2d40db3babe2068156</t>
-  </si>
-  <si>
-    <t>41ef63d5d0665428b088973efcbf524ca04fae91</t>
-  </si>
-  <si>
-    <t>178ee2004b77c19f221f0c21e6cb7c79380f00e0</t>
-  </si>
-  <si>
-    <t>58c8a7dbc2af4112579abf00b21d060b43018e72</t>
-  </si>
-  <si>
-    <t>0fa162876f9045456a2d3f326fccd28b070ab72b</t>
-  </si>
-  <si>
-    <t>5b816120860fa13ee7e0e4515d605cf1f015ffbf</t>
+    <t>73ffd61808e63a4027f14081837e5714a341556d</t>
+  </si>
+  <si>
+    <t>a78bf4837872359efa4b2f7add374b02d50abd24</t>
+  </si>
+  <si>
+    <t>638aed738395a345f4d46bb539acb044d0ac2a83</t>
+  </si>
+  <si>
+    <t>7d9785ad790058e39f66f6b0394ebfd4f38d65a6</t>
+  </si>
+  <si>
+    <t>a827109ebfc68ac935096749d5261ab14a28a88d</t>
+  </si>
+  <si>
+    <t>134b8e417b566e502e68d3ae077ef8cc8cd2791e</t>
+  </si>
+  <si>
+    <t>7547612bfbb13a471cc934cbadde279a2f299ae3</t>
+  </si>
+  <si>
+    <t>023bc70fd79d541f895da053cf7c4cca2920f037</t>
+  </si>
+  <si>
+    <t>d27536ffc1e240c04396616537f41ae34c7965cc</t>
+  </si>
+  <si>
+    <t>e40d1f105e5b5b35fe65f66262bfbed92a22e209</t>
+  </si>
+  <si>
+    <t>7255d25681ca3e3858fe1a1443bc324b34e5b524</t>
+  </si>
+  <si>
+    <t>b1f6110406abdbb0ae0532438d77acd98681a122</t>
+  </si>
+  <si>
+    <t>c5909e4672e3c6a2aaee23c38be246f51e614c34</t>
+  </si>
+  <si>
+    <t>047252d4fc12119a64dfb1598715453566cb9165</t>
   </si>
   <si>
     <t>ccff80daf179b5d57ecd630569568f979a1c63ff</t>
@@ -317,49 +494,22 @@
     <t>5d1c26c738225868e14ce779ae312da0d11f48be</t>
   </si>
   <si>
-    <t>c015b68db87e5d3a8cc56eed805cb80928c34a09</t>
-  </si>
-  <si>
-    <t>2321829cc326287c1d16c7c2d2320566a4c39219</t>
-  </si>
-  <si>
-    <t>24402eaeef5b921d63febaf21127922582c95aa5</t>
-  </si>
-  <si>
-    <t>728e20ff230d675779e3bb40aa72f1742adbdbc7</t>
-  </si>
-  <si>
-    <t>a65f1dae9bf45dbc2e38eb504a0e476107046cd3</t>
-  </si>
-  <si>
-    <t>984145045883d730095faeeff1e1516b19b1082a</t>
-  </si>
-  <si>
-    <t>8dd21005d526da50a06efe1b94b5e6652187e141</t>
-  </si>
-  <si>
-    <t>b70c0908b4f7810a8c4cc855ffdc7e49af0806c2</t>
-  </si>
-  <si>
-    <t>f02685a11cf475251834fb29337a1ef60ee9468e</t>
-  </si>
-  <si>
-    <t>7d9785ad790058e39f66f6b0394ebfd4f38d65a6</t>
-  </si>
-  <si>
-    <t>a827109ebfc68ac935096749d5261ab14a28a88d</t>
-  </si>
-  <si>
-    <t>134b8e417b566e502e68d3ae077ef8cc8cd2791e</t>
-  </si>
-  <si>
-    <t>73ffd61808e63a4027f14081837e5714a341556d</t>
-  </si>
-  <si>
-    <t>a78bf4837872359efa4b2f7add374b02d50abd24</t>
-  </si>
-  <si>
-    <t>638aed738395a345f4d46bb539acb044d0ac2a83</t>
+    <t>6a86386f607506460a7f69b7503ac9fe752890c9</t>
+  </si>
+  <si>
+    <t>6311bbbf021d3d8bba40f6fa719bda8bd9a9ee50</t>
+  </si>
+  <si>
+    <t>4249528d0fb20655eb5353ba46ab614e5c9ecc6d</t>
+  </si>
+  <si>
+    <t>2b8334018afe1dbb35f7499d8910ef4b2914beca</t>
+  </si>
+  <si>
+    <t>18b63f4e05bb5e4695a9c0e2696839b58dac6e06</t>
+  </si>
+  <si>
+    <t>50e47434bbdd0419e8c8113673a2b148e7ce03ef</t>
   </si>
   <si>
     <t>d97e54b5cd2fab349f2d5bb08fd9dea4553b3786</t>
@@ -369,6 +519,354 @@
   </si>
   <si>
     <t>e893caf3adb580e2082ffbf187720ca4250274c2</t>
+  </si>
+  <si>
+    <t>7c3dacc8754f1b4e3fe7c72a90546772b3b3c155</t>
+  </si>
+  <si>
+    <t>527a6351557ffe210cc4fbac27f7c3ed8d9e353d</t>
+  </si>
+  <si>
+    <t>e5c036a60d85093f3b473c0c4d93a5b4857e466b</t>
+  </si>
+  <si>
+    <t>d97f76cd8bee820cf2055075bdc088170e793646</t>
+  </si>
+  <si>
+    <t>cc1c0b62a384fd77999ace3ff162a7a3e48181fb</t>
+  </si>
+  <si>
+    <t>6c325d99e779cf783df6ad5afc42b6459c96edf8</t>
+  </si>
+  <si>
+    <t>cce77b8add5ff105f127e95e1766e28b73491db7</t>
+  </si>
+  <si>
+    <t>b4087e751306ddd7110c5d3af14ec14bfd7553ab</t>
+  </si>
+  <si>
+    <t>45095b524fcf15573375c0037dc066eef068e018</t>
+  </si>
+  <si>
+    <t>14c49629b78b5e09375a6cf32cc4185247f50909</t>
+  </si>
+  <si>
+    <t>2cda46df2a1383ed82d5d56e7a52c823a78f7dfb</t>
+  </si>
+  <si>
+    <t>90d006b4c9f96fb4eb510bfca010f6bf611b8d3d</t>
+  </si>
+  <si>
+    <t>b0dbd40666b9c74c67cc7e735344c3b3feabc2bf</t>
+  </si>
+  <si>
+    <t>1b6f99deb96972dac9cb5c297d461e869de701ee</t>
+  </si>
+  <si>
+    <t>64cdc5f456610e4618799758c613c31a2c45e76e</t>
+  </si>
+  <si>
+    <t>cf4cbe2f57ebbe8b23889bb71887db769c1c4b61</t>
+  </si>
+  <si>
+    <t>0536fa3957fae1257f59ddab3049ee364632f96f</t>
+  </si>
+  <si>
+    <t>496c7880c84ac07bc38c3fffb1454cad3764fac8</t>
+  </si>
+  <si>
+    <t>c0df6eab4e9d8c86496535baf77fb7d960e8dae1</t>
+  </si>
+  <si>
+    <t>906287be21c3f53797e5b15fcbb5b1af15558b04</t>
+  </si>
+  <si>
+    <t>6a283eee895be899319e2c427246b96dbaa090eb</t>
+  </si>
+  <si>
+    <t>398171a40222fee9459e60b86849a688210e4851</t>
+  </si>
+  <si>
+    <t>628cfe22969c56b65342f76a9eb0d16523af951d</t>
+  </si>
+  <si>
+    <t>edcb29d4c69e0fc5ac07454c9eb20cec3967f75c</t>
+  </si>
+  <si>
+    <t>9a49b84f278b1bcedfacb150d32337265ed1765a</t>
+  </si>
+  <si>
+    <t>156818d1c414aa02db6b0167c431273c91f01cb7</t>
+  </si>
+  <si>
+    <t>ad2cc100d24e81754c22622898d926f7e1b331ef</t>
+  </si>
+  <si>
+    <t>c3ac4384faa34ff13a1ac85d814c80b39c9ca214</t>
+  </si>
+  <si>
+    <t>68f6270f6a7cdd18642b52f4fee6c8c33024f832</t>
+  </si>
+  <si>
+    <t>76e85018f01b243cf061d83718c2df877f81530f</t>
+  </si>
+  <si>
+    <t>4ca68ff56ad735d6d405d8842c86beffb0482f0c</t>
+  </si>
+  <si>
+    <t>a9d91250f5c576a4ab95b60d1070653c2f4c58a8</t>
+  </si>
+  <si>
+    <t>63393108e922031288d367f1a6150b7575aa3f11</t>
+  </si>
+  <si>
+    <t>b8f1d01733535068402e11f1383e922e5c66d4e9</t>
+  </si>
+  <si>
+    <t>b160d409f3e214b7acaace92e2c2061345671432</t>
+  </si>
+  <si>
+    <t>f63b75241bf05203afc2bc464476bbfba7e14692</t>
+  </si>
+  <si>
+    <t>daef8d3b031656b69a43e937de8d076749a7f639</t>
+  </si>
+  <si>
+    <t>cef4c142865ed06280a40221e19929aec7794943</t>
+  </si>
+  <si>
+    <t>96b3188c3ef092373ea6ead71a592cea416822eb</t>
+  </si>
+  <si>
+    <t>413976913159b116ad9c80f76d23055b042df805</t>
+  </si>
+  <si>
+    <t>0ee01346d0630078adcf549d4c606eb6b7110f75</t>
+  </si>
+  <si>
+    <t>4ca583cbe8ed81f14603068d66bc54a64a611024</t>
+  </si>
+  <si>
+    <t>d1e13f4b82cbc2b50cff5b25b21216281ebbf326</t>
+  </si>
+  <si>
+    <t>4e200c57f7fea070c44d6514c495e86c92eaf4d7</t>
+  </si>
+  <si>
+    <t>c940d6b48ec7a274d9208f745ac1d416cb0bbcba</t>
+  </si>
+  <si>
+    <t>87955a97512bfc53f376cfbab2e29ab84bd25292</t>
+  </si>
+  <si>
+    <t>b1c11f8dd87b3e61239183899e8310ae654e85a5</t>
+  </si>
+  <si>
+    <t>0f802a6b524e85fa959d648c9101a56323188561</t>
+  </si>
+  <si>
+    <t>b500bb7da134ae76a8a169bec8d64daaa07b4f13</t>
+  </si>
+  <si>
+    <t>ac6ebbf421db87ee82af0036d975cae830fda60a</t>
+  </si>
+  <si>
+    <t>373c780fee7de2df2d5df4a6e4720e9cf0369d48</t>
+  </si>
+  <si>
+    <t>720b426f5ee0eb9832c46d63869f8ddaf0956277</t>
+  </si>
+  <si>
+    <t>b026d186a6a708cd0420193a8411faba9ec4e3fb</t>
+  </si>
+  <si>
+    <t>61ebfc79a15812f9763c9e43346e6eb4df5a1096</t>
+  </si>
+  <si>
+    <t>5fc4b5a64bf7d2919e6fde6136c7bf03eda05254</t>
+  </si>
+  <si>
+    <t>6a20f3cb89472310b84e12cd516f92222cbe1fb3</t>
+  </si>
+  <si>
+    <t>5bc59091941c5b15d266e00a87d47505aa2b69dd</t>
+  </si>
+  <si>
+    <t>76e4586e208d2081d7db5fb866adad7c893c7428</t>
+  </si>
+  <si>
+    <t>88c5c7fdf7fa026f192591fe83bbaff0ddfd3703</t>
+  </si>
+  <si>
+    <t>be67194cfb6d97581adfb7b7b47402093944c9df</t>
+  </si>
+  <si>
+    <t>468d4cc6f621c454e59092e994cb55c4613ff8e5</t>
+  </si>
+  <si>
+    <t>a9837ae8fe2f080e97af461bb0e68214d9d5a2f8</t>
+  </si>
+  <si>
+    <t>a981ad6e1ca94be04aa827e8115f69ec84cf275e</t>
+  </si>
+  <si>
+    <t>b90ea83d2caed23f77201b185c9fedb9b4809631</t>
+  </si>
+  <si>
+    <t>7766c82f6c0d38cbdbcb2ea95f0c812bf40589f9</t>
+  </si>
+  <si>
+    <t>bb5966f1b694737e8c96d6824a2d5093fe58adf3</t>
+  </si>
+  <si>
+    <t>503a6eecc517b5c92e120496010cdbab31fa20ea</t>
+  </si>
+  <si>
+    <t>76a25f02832bb2b37cb8ef3e40eef38bc5639691</t>
+  </si>
+  <si>
+    <t>684c249d4ba7d1cc919453925703e072174d79e1</t>
+  </si>
+  <si>
+    <t>c0b196bd07797f4e9be6f60b846d1af9bc6261fe</t>
+  </si>
+  <si>
+    <t>a8a134063f90b9a4940173018eb73f63ed15d067</t>
+  </si>
+  <si>
+    <t>3b8675dc6a34db87f6aed9e35b51532d359fe502</t>
+  </si>
+  <si>
+    <t>be6aaec8182ea9e6306af23e88ecd9777b0ec4ab</t>
+  </si>
+  <si>
+    <t>60d56f08341f08baccb606f512fc2167f44db2d0</t>
+  </si>
+  <si>
+    <t>e2c1c7d3805b2ef487f22ef41267dfb9ea53e255</t>
+  </si>
+  <si>
+    <t>809e6961d67cd31b38bcaf07c7f7770a792ef99c</t>
+  </si>
+  <si>
+    <t>68fef349e50f312e3c74b4fcf8a8ad72e0fbefc9</t>
+  </si>
+  <si>
+    <t>188f98eaa2a9808879243599b7e984f503a9541f</t>
+  </si>
+  <si>
+    <t>38135a1792f961954b0d4be0623e25b4e06e0e75</t>
+  </si>
+  <si>
+    <t>e1df64db3cffbc0e5b321c41ce95843d0bee419b</t>
+  </si>
+  <si>
+    <t>f88c07af179b10d2b45a9de4c24476c81a01478b</t>
+  </si>
+  <si>
+    <t>93163f6c07f2259a881cb2345e5a8b41499e335d</t>
+  </si>
+  <si>
+    <t>910bbe8400b298a6cbbc3b02ddff1903a586a2ce</t>
+  </si>
+  <si>
+    <t>44e03eae83b44b87c1f28fdfcfdac75155a46435</t>
+  </si>
+  <si>
+    <t>59178eca49134d8f58f3356ab1f6b8b3e008fc90</t>
+  </si>
+  <si>
+    <t>44055ba53f77c1e87914c12b39f8692fd5187e0e</t>
+  </si>
+  <si>
+    <t>961e3210c746a3951001d59c41860d233455fddb</t>
+  </si>
+  <si>
+    <t>820f185085f2e165fd6020683f249e795e157850</t>
+  </si>
+  <si>
+    <t>148adb4e318f21c9c78a75c8ddbc72763377fe76</t>
+  </si>
+  <si>
+    <t>ec92874cf495cfcfc37e37ac76304c5343df56a7</t>
+  </si>
+  <si>
+    <t>d82df8154a154ab78880abb8a74b4f46ed408509</t>
+  </si>
+  <si>
+    <t>aa85fff2957195e46204c616e793cedcfc808e94</t>
+  </si>
+  <si>
+    <t>9258b67097e1eca05e29f17f64bf0e7d17d05d5a</t>
+  </si>
+  <si>
+    <t>5e3e68f7f5d911ce6284870ea219c56b0b4bc308</t>
+  </si>
+  <si>
+    <t>96e25482405b438d326ed54a508df9eaf7804334</t>
+  </si>
+  <si>
+    <t>b150605da9c7d6c8bea1c1c68bea8c5c3d24686c</t>
+  </si>
+  <si>
+    <t>c41a155cfe99923604bda3b648c0ffc2fdee3d09</t>
+  </si>
+  <si>
+    <t>9d6eca05dd8688ba420b97185cd6b57322a07b60</t>
+  </si>
+  <si>
+    <t>9de92e730b53479ab5537589cdad0c95f2034b30</t>
+  </si>
+  <si>
+    <t>8e17192ad16a6c644785ef31ca78e6e976e91dc0</t>
+  </si>
+  <si>
+    <t>ea4db88dab3a42d8154856305120b167cfa39a35</t>
+  </si>
+  <si>
+    <t>819ad49b089cd32fb9d77d670f764c809c18a7eb</t>
+  </si>
+  <si>
+    <t>59dd0a3f5c0258652b09fb920bbb055042d537c0</t>
+  </si>
+  <si>
+    <t>e618f833fd50d01cad442c3192d2473fa444d45c</t>
+  </si>
+  <si>
+    <t>2bd9fd97bba1197846ce9422fc6a00ba58e6d9f5</t>
+  </si>
+  <si>
+    <t>d1ed44529891babf642b27b9dd24977a8c110d81</t>
+  </si>
+  <si>
+    <t>328445f7c0afdb82b383aae09d30d0aa8fc7306e</t>
+  </si>
+  <si>
+    <t>06bfe3335e93d83eeebdc96bbea26c55eaaeb7ef</t>
+  </si>
+  <si>
+    <t>3192a252cdbbd9290e9301b60b35b297b1774316</t>
+  </si>
+  <si>
+    <t>911790ad16a8ba0427089eecc55810e78e5ea41b</t>
+  </si>
+  <si>
+    <t>86e5149ac6a127787ff533c1eaed40644da88d2a</t>
+  </si>
+  <si>
+    <t>d10e5fc63fa1cf97aa1589ce6534442e2c4c38c3</t>
+  </si>
+  <si>
+    <t>61d8836c2d5ab8898481d3b051c0e0f364382b41</t>
+  </si>
+  <si>
+    <t>9d8f924fec21e53f2de188bedfa72973e880b28f</t>
+  </si>
+  <si>
+    <t>a015b1e5393ac5c93cdf9961c414c4763c1c3f6e</t>
+  </si>
+  <si>
+    <t>6d40550bbf1834fac4dc011c6a98c5de3dccfba0</t>
   </si>
 </sst>
 </file>
@@ -413,7 +911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -462,10 +960,10 @@
         <v>1.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G2" t="b" s="0">
         <v>0</v>
@@ -474,10 +972,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>0.125</v>
+        <v>0.1860000044107437</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -491,13 +989,13 @@
         <v>15</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>1.0</v>
+        <v>62.0</v>
       </c>
       <c r="E3" t="n" s="0">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="F3" t="n" s="0">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="G3" t="b" s="0">
         <v>0</v>
@@ -506,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>0.1289999932050705</v>
+        <v>36.676002502441406</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -523,13 +1021,13 @@
         <v>18</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>1.0</v>
+        <v>171.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="F4" t="n" s="0">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G4" t="b" s="0">
         <v>0</v>
@@ -538,10 +1036,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>0.3619999885559082</v>
+        <v>107.17499542236328</v>
       </c>
       <c r="J4" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -555,13 +1053,13 @@
         <v>21</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>2.0</v>
+        <v>171.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G5" t="b" s="0">
         <v>0</v>
@@ -570,10 +1068,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>4.091000080108643</v>
+        <v>102.61499786376953</v>
       </c>
       <c r="J5" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -587,10 +1085,10 @@
         <v>24</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>50.0</v>
+        <v>54.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>17.0</v>
+        <v>5.0</v>
       </c>
       <c r="F6" t="n" s="0">
         <v>5.0</v>
@@ -602,10 +1100,10 @@
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>102.58499908447266</v>
+        <v>24.854000091552734</v>
       </c>
       <c r="J6" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -619,13 +1117,13 @@
         <v>27</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>50.0</v>
+        <v>2.0</v>
       </c>
       <c r="E7" t="n" s="0">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
       <c r="F7" t="n" s="0">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
       <c r="G7" t="b" s="0">
         <v>0</v>
@@ -634,10 +1132,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>26.05699920654297</v>
+        <v>4.541999816894531</v>
       </c>
       <c r="J7" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -651,13 +1149,13 @@
         <v>30</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>1.0</v>
+        <v>389.0</v>
       </c>
       <c r="E8" t="n" s="0">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="F8" t="n" s="0">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G8" t="b" s="0">
         <v>0</v>
@@ -666,10 +1164,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>0.2770000100135803</v>
+        <v>225.30999755859375</v>
       </c>
       <c r="J8" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -683,13 +1181,13 @@
         <v>33</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>50.0</v>
+        <v>455.0</v>
       </c>
       <c r="E9" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G9" t="b" s="0">
         <v>0</v>
@@ -698,10 +1196,10 @@
         <v>1</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>83.281005859375</v>
+        <v>170.74200439453125</v>
       </c>
       <c r="J9" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -715,13 +1213,13 @@
         <v>36</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>45.0</v>
+        <v>1.0</v>
       </c>
       <c r="E10" t="n" s="0">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F10" t="n" s="0">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G10" t="b" s="0">
         <v>0</v>
@@ -730,10 +1228,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n" s="0">
-        <v>47.06500244140625</v>
+        <v>0.29899999499320984</v>
       </c>
       <c r="J10" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -741,19 +1239,19 @@
         <v>37</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>60.0</v>
+        <v>792.0</v>
       </c>
       <c r="E11" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F11" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G11" t="b" s="0">
         <v>0</v>
@@ -762,30 +1260,30 @@
         <v>1</v>
       </c>
       <c r="I11" t="n" s="0">
-        <v>71.6510009765625</v>
+        <v>336.780029296875</v>
       </c>
       <c r="J11" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>1.0</v>
+        <v>823.0</v>
       </c>
       <c r="E12" t="n" s="0">
-        <v>10.0</v>
+        <v>105.0</v>
       </c>
       <c r="F12" t="n" s="0">
-        <v>10.0</v>
+        <v>101.0</v>
       </c>
       <c r="G12" t="b" s="0">
         <v>0</v>
@@ -794,30 +1292,30 @@
         <v>1</v>
       </c>
       <c r="I12" t="n" s="0">
-        <v>0.4169999957084656</v>
+        <v>346.67095947265625</v>
       </c>
       <c r="J12" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>174.0</v>
+        <v>837.0</v>
       </c>
       <c r="E13" t="n" s="0">
-        <v>105.0</v>
+        <v>1.0</v>
       </c>
       <c r="F13" t="n" s="0">
-        <v>101.0</v>
+        <v>1.0</v>
       </c>
       <c r="G13" t="b" s="0">
         <v>0</v>
@@ -826,24 +1324,24 @@
         <v>1</v>
       </c>
       <c r="I13" t="n" s="0">
-        <v>201.82701110839844</v>
+        <v>361.009033203125</v>
       </c>
       <c r="J13" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>185.0</v>
+        <v>1003.0</v>
       </c>
       <c r="E14" t="n" s="0">
         <v>1.0</v>
@@ -858,30 +1356,30 @@
         <v>1</v>
       </c>
       <c r="I14" t="n" s="0">
-        <v>272.7039794921875</v>
+        <v>374.9840393066406</v>
       </c>
       <c r="J14" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>349.0</v>
+        <v>1003.0</v>
       </c>
       <c r="E15" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F15" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G15" t="b" s="0">
         <v>0</v>
@@ -890,24 +1388,24 @@
         <v>1</v>
       </c>
       <c r="I15" t="n" s="0">
-        <v>195.0980224609375</v>
+        <v>365.26104736328125</v>
       </c>
       <c r="J15" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>176.0</v>
+        <v>1.0</v>
       </c>
       <c r="E16" t="n" s="0">
         <v>1.0</v>
@@ -922,30 +1420,30 @@
         <v>1</v>
       </c>
       <c r="I16" t="n" s="0">
-        <v>347.84808349609375</v>
+        <v>0.2070000022649765</v>
       </c>
       <c r="J16" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>174.0</v>
+        <v>1003.0</v>
       </c>
       <c r="E17" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F17" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G17" t="b" s="0">
         <v>0</v>
@@ -954,30 +1452,30 @@
         <v>1</v>
       </c>
       <c r="I17" t="n" s="0">
-        <v>342.1490173339844</v>
+        <v>372.5770263671875</v>
       </c>
       <c r="J17" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>45.0</v>
+        <v>828.0</v>
       </c>
       <c r="E18" t="n" s="0">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="F18" t="n" s="0">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G18" t="b" s="0">
         <v>0</v>
@@ -986,30 +1484,30 @@
         <v>1</v>
       </c>
       <c r="I18" t="n" s="0">
-        <v>46.599998474121094</v>
+        <v>367.8871154785156</v>
       </c>
       <c r="J18" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>107.0</v>
+        <v>377.0</v>
       </c>
       <c r="E19" t="n" s="0">
-        <v>44.0</v>
+        <v>1.0</v>
       </c>
       <c r="F19" t="n" s="0">
-        <v>44.0</v>
+        <v>1.0</v>
       </c>
       <c r="G19" t="b" s="0">
         <v>0</v>
@@ -1018,30 +1516,30 @@
         <v>1</v>
       </c>
       <c r="I19" t="n" s="0">
-        <v>122.35999298095703</v>
+        <v>227.22198486328125</v>
       </c>
       <c r="J19" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B20" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>111.0</v>
+        <v>825.0</v>
       </c>
       <c r="E20" t="n" s="0">
-        <v>23.0</v>
+        <v>1.0</v>
       </c>
       <c r="F20" t="n" s="0">
-        <v>22.0</v>
+        <v>1.0</v>
       </c>
       <c r="G20" t="b" s="0">
         <v>0</v>
@@ -1050,30 +1548,30 @@
         <v>1</v>
       </c>
       <c r="I20" t="n" s="0">
-        <v>421.96002197265625</v>
+        <v>338.6910400390625</v>
       </c>
       <c r="J20" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B21" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>71.0</v>
+        <v>60.0</v>
       </c>
       <c r="E21" t="n" s="0">
-        <v>12.0</v>
+        <v>17.0</v>
       </c>
       <c r="F21" t="n" s="0">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="G21" t="b" s="0">
         <v>0</v>
@@ -1082,30 +1580,30 @@
         <v>1</v>
       </c>
       <c r="I21" t="n" s="0">
-        <v>177.3090057373047</v>
+        <v>52.24300003051758</v>
       </c>
       <c r="J21" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s" s="0">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s" s="0">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>174.0</v>
+        <v>1.0</v>
       </c>
       <c r="E22" t="n" s="0">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="F22" t="n" s="0">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G22" t="b" s="0">
         <v>0</v>
@@ -1114,30 +1612,30 @@
         <v>1</v>
       </c>
       <c r="I22" t="n" s="0">
-        <v>294.09002685546875</v>
+        <v>0.12600000202655792</v>
       </c>
       <c r="J22" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B23" t="s" s="0">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s" s="0">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>10.0</v>
+        <v>104.0</v>
       </c>
       <c r="E23" t="n" s="0">
-        <v>26.0</v>
+        <v>18.0</v>
       </c>
       <c r="F23" t="n" s="0">
-        <v>26.0</v>
+        <v>18.0</v>
       </c>
       <c r="G23" t="b" s="0">
         <v>0</v>
@@ -1146,24 +1644,24 @@
         <v>1</v>
       </c>
       <c r="I23" t="n" s="0">
-        <v>44.573001861572266</v>
+        <v>69.10000610351562</v>
       </c>
       <c r="J23" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B24" t="s" s="0">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>349.0</v>
+        <v>60.0</v>
       </c>
       <c r="E24" t="n" s="0">
         <v>1.0</v>
@@ -1178,30 +1676,30 @@
         <v>1</v>
       </c>
       <c r="I24" t="n" s="0">
-        <v>304.031982421875</v>
+        <v>70.1409912109375</v>
       </c>
       <c r="J24" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B25" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>185.0</v>
+        <v>277.0</v>
       </c>
       <c r="E25" t="n" s="0">
-        <v>3.0</v>
+        <v>44.0</v>
       </c>
       <c r="F25" t="n" s="0">
-        <v>2.0</v>
+        <v>44.0</v>
       </c>
       <c r="G25" t="b" s="0">
         <v>0</v>
@@ -1210,24 +1708,24 @@
         <v>1</v>
       </c>
       <c r="I25" t="n" s="0">
-        <v>194.64198303222656</v>
+        <v>170.83401489257812</v>
       </c>
       <c r="J25" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B26" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>111.0</v>
+        <v>98.0</v>
       </c>
       <c r="E26" t="n" s="0">
         <v>1.0</v>
@@ -1242,24 +1740,24 @@
         <v>1</v>
       </c>
       <c r="I26" t="n" s="0">
-        <v>325.27899169921875</v>
+        <v>43.47800064086914</v>
       </c>
       <c r="J26" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>124.0</v>
+        <v>659.0</v>
       </c>
       <c r="E27" t="n" s="0">
         <v>3.0</v>
@@ -1274,30 +1772,30 @@
         <v>1</v>
       </c>
       <c r="I27" t="n" s="0">
-        <v>473.7440185546875</v>
+        <v>314.2769775390625</v>
       </c>
       <c r="J27" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B28" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>1.0</v>
+        <v>779.0</v>
       </c>
       <c r="E28" t="n" s="0">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="F28" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G28" t="b" s="0">
         <v>0</v>
@@ -1306,30 +1804,30 @@
         <v>1</v>
       </c>
       <c r="I28" t="n" s="0">
-        <v>0.24199999868869781</v>
+        <v>318.7449951171875</v>
       </c>
       <c r="J28" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B29" t="s" s="0">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s" s="0">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>111.0</v>
+        <v>1.0</v>
       </c>
       <c r="E29" t="n" s="0">
-        <v>1208.0</v>
+        <v>10.0</v>
       </c>
       <c r="F29" t="n" s="0">
-        <v>1157.0</v>
+        <v>10.0</v>
       </c>
       <c r="G29" t="b" s="0">
         <v>0</v>
@@ -1338,24 +1836,24 @@
         <v>1</v>
       </c>
       <c r="I29" t="n" s="0">
-        <v>458.552001953125</v>
+        <v>0.17900000512599945</v>
       </c>
       <c r="J29" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B30" t="s" s="0">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="C30" t="s" s="0">
         <v>94</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>176.0</v>
+        <v>824.0</v>
       </c>
       <c r="E30" t="n" s="0">
         <v>1.0</v>
@@ -1370,10 +1868,10 @@
         <v>1</v>
       </c>
       <c r="I30" t="n" s="0">
-        <v>583.39697265625</v>
+        <v>367.1920166015625</v>
       </c>
       <c r="J30" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1387,13 +1885,13 @@
         <v>97</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>111.0</v>
+        <v>779.0</v>
       </c>
       <c r="E31" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F31" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G31" t="b" s="0">
         <v>0</v>
@@ -1402,10 +1900,10 @@
         <v>1</v>
       </c>
       <c r="I31" t="n" s="0">
-        <v>215.40902709960938</v>
+        <v>324.9670104980469</v>
       </c>
       <c r="J31" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1419,13 +1917,13 @@
         <v>100</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>103.0</v>
+        <v>690.0</v>
       </c>
       <c r="E32" t="n" s="0">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
       <c r="F32" t="n" s="0">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G32" t="b" s="0">
         <v>0</v>
@@ -1434,10 +1932,10 @@
         <v>1</v>
       </c>
       <c r="I32" t="n" s="0">
-        <v>139.50999450683594</v>
+        <v>286.18206787109375</v>
       </c>
       <c r="J32" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1451,13 +1949,13 @@
         <v>103</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>179.0</v>
+        <v>601.0</v>
       </c>
       <c r="E33" t="n" s="0">
-        <v>7.0</v>
+        <v>1208.0</v>
       </c>
       <c r="F33" t="n" s="0">
-        <v>5.0</v>
+        <v>1157.0</v>
       </c>
       <c r="G33" t="b" s="0">
         <v>0</v>
@@ -1466,10 +1964,10 @@
         <v>1</v>
       </c>
       <c r="I33" t="n" s="0">
-        <v>465.68402099609375</v>
+        <v>270.822998046875</v>
       </c>
       <c r="J33" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1483,13 +1981,13 @@
         <v>106</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>103.0</v>
+        <v>645.0</v>
       </c>
       <c r="E34" t="n" s="0">
-        <v>2.0</v>
+        <v>23.0</v>
       </c>
       <c r="F34" t="n" s="0">
-        <v>2.0</v>
+        <v>22.0</v>
       </c>
       <c r="G34" t="b" s="0">
         <v>0</v>
@@ -1498,10 +1996,10 @@
         <v>1</v>
       </c>
       <c r="I34" t="n" s="0">
-        <v>267.9620056152344</v>
+        <v>326.9740905761719</v>
       </c>
       <c r="J34" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1515,7 +2013,7 @@
         <v>109</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>111.0</v>
+        <v>645.0</v>
       </c>
       <c r="E35" t="n" s="0">
         <v>1.0</v>
@@ -1530,10 +2028,10 @@
         <v>1</v>
       </c>
       <c r="I35" t="n" s="0">
-        <v>129.41099548339844</v>
+        <v>307.1109924316406</v>
       </c>
       <c r="J35" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1547,7 +2045,7 @@
         <v>112</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>1.0</v>
+        <v>55.0</v>
       </c>
       <c r="E36" t="n" s="0">
         <v>26.0</v>
@@ -1562,10 +2060,10 @@
         <v>1</v>
       </c>
       <c r="I36" t="n" s="0">
-        <v>0.4189999997615814</v>
+        <v>30.735000610351562</v>
       </c>
       <c r="J36" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1579,13 +2077,13 @@
         <v>115</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>103.0</v>
+        <v>780.0</v>
       </c>
       <c r="E37" t="n" s="0">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="F37" t="n" s="0">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G37" t="b" s="0">
         <v>0</v>
@@ -1594,10 +2092,10 @@
         <v>1</v>
       </c>
       <c r="I37" t="n" s="0">
-        <v>248.1160125732422</v>
+        <v>371.3400573730469</v>
       </c>
       <c r="J37" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1611,7 +2109,7 @@
         <v>118</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>1.0</v>
+        <v>780.0</v>
       </c>
       <c r="E38" t="n" s="0">
         <v>1.0</v>
@@ -1626,10 +2124,1834 @@
         <v>1</v>
       </c>
       <c r="I38" t="n" s="0">
-        <v>0.30399999022483826</v>
+        <v>375.41302490234375</v>
       </c>
       <c r="J38" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="D39" t="n" s="0">
+        <v>323.0</v>
+      </c>
+      <c r="E39" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F39" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G39" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H39" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n" s="0">
+        <v>235.60000610351562</v>
+      </c>
+      <c r="J39" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="D40" t="n" s="0">
+        <v>323.0</v>
+      </c>
+      <c r="E40" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="F40" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="G40" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H40" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n" s="0">
+        <v>244.00601196289062</v>
+      </c>
+      <c r="J40" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="D41" t="n" s="0">
+        <v>323.0</v>
+      </c>
+      <c r="E41" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F41" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G41" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H41" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n" s="0">
+        <v>245.52198791503906</v>
+      </c>
+      <c r="J41" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="D42" t="n" s="0">
+        <v>279.0</v>
+      </c>
+      <c r="E42" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F42" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G42" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H42" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n" s="0">
+        <v>195.78701782226562</v>
+      </c>
+      <c r="J42" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="D43" t="n" s="0">
+        <v>780.0</v>
+      </c>
+      <c r="E43" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F43" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G43" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H43" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n" s="0">
+        <v>400.4119873046875</v>
+      </c>
+      <c r="J43" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="D44" t="n" s="0">
+        <v>691.0</v>
+      </c>
+      <c r="E44" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F44" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G44" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H44" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n" s="0">
+        <v>310.44091796875</v>
+      </c>
+      <c r="J44" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="D45" t="n" s="0">
+        <v>729.0</v>
+      </c>
+      <c r="E45" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F45" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G45" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H45" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n" s="0">
+        <v>325.5369873046875</v>
+      </c>
+      <c r="J45" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="D46" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E46" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="F46" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="G46" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H46" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n" s="0">
+        <v>0.12700000405311584</v>
+      </c>
+      <c r="J46" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="D47" t="n" s="0">
+        <v>729.0</v>
+      </c>
+      <c r="E47" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="F47" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="G47" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H47" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n" s="0">
+        <v>336.2720642089844</v>
+      </c>
+      <c r="J47" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="D48" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E48" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="F48" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="G48" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H48" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n" s="0">
+        <v>0.33799999952316284</v>
+      </c>
+      <c r="J48" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="D49" t="n" s="0">
+        <v>729.0</v>
+      </c>
+      <c r="E49" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F49" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G49" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H49" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n" s="0">
+        <v>324.13299560546875</v>
+      </c>
+      <c r="J49" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="D50" t="n" s="0">
+        <v>55.0</v>
+      </c>
+      <c r="E50" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F50" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G50" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H50" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I50" t="n" s="0">
+        <v>35.14400100708008</v>
+      </c>
+      <c r="J50" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="D51" t="n" s="0">
+        <v>55.0</v>
+      </c>
+      <c r="E51" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F51" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G51" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H51" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n" s="0">
+        <v>34.520999908447266</v>
+      </c>
+      <c r="J51" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="D52" t="n" s="0">
+        <v>730.0</v>
+      </c>
+      <c r="E52" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F52" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G52" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H52" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n" s="0">
+        <v>335.9100036621094</v>
+      </c>
+      <c r="J52" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="D53" t="n" s="0">
+        <v>106.0</v>
+      </c>
+      <c r="E53" t="n" s="0">
+        <v>56.0</v>
+      </c>
+      <c r="F53" t="n" s="0">
+        <v>56.0</v>
+      </c>
+      <c r="G53" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H53" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I53" t="n" s="0">
+        <v>81.14400482177734</v>
+      </c>
+      <c r="J53" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="D54" t="n" s="0">
+        <v>639.0</v>
+      </c>
+      <c r="E54" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="F54" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="G54" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H54" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I54" t="n" s="0">
+        <v>318.1860046386719</v>
+      </c>
+      <c r="J54" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="D55" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E55" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F55" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G55" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H55" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n" s="0">
+        <v>0.08500000089406967</v>
+      </c>
+      <c r="J55" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>169</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>171</v>
+      </c>
+      <c r="D56" t="n" s="0">
+        <v>730.0</v>
+      </c>
+      <c r="E56" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F56" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="G56" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H56" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I56" t="n" s="0">
+        <v>326.2540283203125</v>
+      </c>
+      <c r="J56" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>172</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="C57" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="D57" t="n" s="0">
+        <v>279.0</v>
+      </c>
+      <c r="E57" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="F57" t="n" s="0">
+        <v>26.0</v>
+      </c>
+      <c r="G57" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H57" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n" s="0">
+        <v>205.44102478027344</v>
+      </c>
+      <c r="J57" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>175</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>176</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="D58" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E58" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="F58" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="G58" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H58" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n" s="0">
+        <v>0.08399999886751175</v>
+      </c>
+      <c r="J58" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="C59" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="D59" t="n" s="0">
+        <v>730.0</v>
+      </c>
+      <c r="E59" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="F59" t="n" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="G59" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H59" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I59" t="n" s="0">
+        <v>311.43701171875</v>
+      </c>
+      <c r="J59" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>181</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>182</v>
+      </c>
+      <c r="D60" t="n" s="0">
+        <v>760.0</v>
+      </c>
+      <c r="E60" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F60" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G60" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H60" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I60" t="n" s="0">
+        <v>362.3290710449219</v>
+      </c>
+      <c r="J60" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>181</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="C61" t="s" s="0">
+        <v>184</v>
+      </c>
+      <c r="D61" t="n" s="0">
+        <v>760.0</v>
+      </c>
+      <c r="E61" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F61" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G61" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H61" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I61" t="n" s="0">
+        <v>366.6820068359375</v>
+      </c>
+      <c r="J61" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>186</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="D62" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E62" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F62" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G62" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H62" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I62" t="n" s="0">
+        <v>0.21899999678134918</v>
+      </c>
+      <c r="J62" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>188</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="C63" t="s" s="0">
+        <v>190</v>
+      </c>
+      <c r="D63" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E63" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F63" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G63" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H63" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n" s="0">
+        <v>0.07599999755620956</v>
+      </c>
+      <c r="J63" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C64" t="s" s="0">
+        <v>193</v>
+      </c>
+      <c r="D64" t="n" s="0">
+        <v>759.0</v>
+      </c>
+      <c r="E64" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F64" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G64" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H64" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I64" t="n" s="0">
+        <v>350.5</v>
+      </c>
+      <c r="J64" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="B65" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C65" t="s" s="0">
+        <v>196</v>
+      </c>
+      <c r="D65" t="n" s="0">
+        <v>759.0</v>
+      </c>
+      <c r="E65" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F65" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G65" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H65" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I65" t="n" s="0">
+        <v>358.12506103515625</v>
+      </c>
+      <c r="J65" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>197</v>
+      </c>
+      <c r="B66" t="s" s="0">
+        <v>198</v>
+      </c>
+      <c r="C66" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="D66" t="n" s="0">
+        <v>174.0</v>
+      </c>
+      <c r="E66" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="F66" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="G66" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H66" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I66" t="n" s="0">
+        <v>168.0509796142578</v>
+      </c>
+      <c r="J66" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="B67" t="s" s="0">
+        <v>201</v>
+      </c>
+      <c r="C67" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="D67" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E67" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="F67" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="G67" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H67" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I67" t="n" s="0">
+        <v>0.09799999743700027</v>
+      </c>
+      <c r="J67" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="C68" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="D68" t="n" s="0">
+        <v>309.0</v>
+      </c>
+      <c r="E68" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F68" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="G68" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H68" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I68" t="n" s="0">
+        <v>218.19497680664062</v>
+      </c>
+      <c r="J68" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="C69" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="D69" t="n" s="0">
+        <v>309.0</v>
+      </c>
+      <c r="E69" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F69" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G69" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H69" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I69" t="n" s="0">
+        <v>223.01600646972656</v>
+      </c>
+      <c r="J69" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="C70" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="D70" t="n" s="0">
+        <v>54.0</v>
+      </c>
+      <c r="E70" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F70" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G70" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H70" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I70" t="n" s="0">
+        <v>25.100000381469727</v>
+      </c>
+      <c r="J70" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="B71" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="C71" t="s" s="0">
+        <v>214</v>
+      </c>
+      <c r="D71" t="n" s="0">
+        <v>748.0</v>
+      </c>
+      <c r="E71" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F71" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G71" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H71" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I71" t="n" s="0">
+        <v>346.4219970703125</v>
+      </c>
+      <c r="J71" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B72" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C72" t="s" s="0">
+        <v>217</v>
+      </c>
+      <c r="D72" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E72" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F72" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G72" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H72" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I72" t="n" s="0">
+        <v>5.503000259399414</v>
+      </c>
+      <c r="J72" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>218</v>
+      </c>
+      <c r="B73" t="s" s="0">
+        <v>219</v>
+      </c>
+      <c r="C73" t="s" s="0">
+        <v>220</v>
+      </c>
+      <c r="D73" t="n" s="0">
+        <v>746.0</v>
+      </c>
+      <c r="E73" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="F73" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="G73" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H73" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I73" t="n" s="0">
+        <v>344.1200256347656</v>
+      </c>
+      <c r="J73" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>221</v>
+      </c>
+      <c r="B74" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="C74" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="D74" t="n" s="0">
+        <v>611.0</v>
+      </c>
+      <c r="E74" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F74" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G74" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H74" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I74" t="n" s="0">
+        <v>273.1240234375</v>
+      </c>
+      <c r="J74" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="B75" t="s" s="0">
+        <v>225</v>
+      </c>
+      <c r="C75" t="s" s="0">
+        <v>226</v>
+      </c>
+      <c r="D75" t="n" s="0">
+        <v>177.0</v>
+      </c>
+      <c r="E75" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F75" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G75" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H75" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I75" t="n" s="0">
+        <v>127.77098846435547</v>
+      </c>
+      <c r="J75" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="0">
+        <v>227</v>
+      </c>
+      <c r="B76" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="C76" t="s" s="0">
+        <v>229</v>
+      </c>
+      <c r="D76" t="n" s="0">
+        <v>611.0</v>
+      </c>
+      <c r="E76" t="n" s="0">
+        <v>76.0</v>
+      </c>
+      <c r="F76" t="n" s="0">
+        <v>75.0</v>
+      </c>
+      <c r="G76" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H76" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n" s="0">
+        <v>280.5350341796875</v>
+      </c>
+      <c r="J76" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="0">
+        <v>186</v>
+      </c>
+      <c r="B77" t="s" s="0">
+        <v>230</v>
+      </c>
+      <c r="C77" t="s" s="0">
+        <v>231</v>
+      </c>
+      <c r="D77" t="n" s="0">
+        <v>746.0</v>
+      </c>
+      <c r="E77" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F77" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G77" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H77" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I77" t="n" s="0">
+        <v>343.6629638671875</v>
+      </c>
+      <c r="J77" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="B78" t="s" s="0">
+        <v>233</v>
+      </c>
+      <c r="C78" t="s" s="0">
+        <v>234</v>
+      </c>
+      <c r="D78" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E78" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F78" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G78" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H78" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I78" t="n" s="0">
+        <v>0.125</v>
+      </c>
+      <c r="J78" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>235</v>
+      </c>
+      <c r="B79" t="s" s="0">
+        <v>236</v>
+      </c>
+      <c r="C79" t="s" s="0">
+        <v>237</v>
+      </c>
+      <c r="D79" t="n" s="0">
+        <v>769.0</v>
+      </c>
+      <c r="E79" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="F79" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="G79" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H79" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I79" t="n" s="0">
+        <v>334.0089416503906</v>
+      </c>
+      <c r="J79" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>238</v>
+      </c>
+      <c r="B80" t="s" s="0">
+        <v>239</v>
+      </c>
+      <c r="C80" t="s" s="0">
+        <v>240</v>
+      </c>
+      <c r="D80" t="n" s="0">
+        <v>314.0</v>
+      </c>
+      <c r="E80" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F80" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G80" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H80" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I80" t="n" s="0">
+        <v>250.9550018310547</v>
+      </c>
+      <c r="J80" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>241</v>
+      </c>
+      <c r="B81" t="s" s="0">
+        <v>242</v>
+      </c>
+      <c r="C81" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="D81" t="n" s="0">
+        <v>54.0</v>
+      </c>
+      <c r="E81" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F81" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G81" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H81" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I81" t="n" s="0">
+        <v>27.69999885559082</v>
+      </c>
+      <c r="J81" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="0">
+        <v>244</v>
+      </c>
+      <c r="B82" t="s" s="0">
+        <v>245</v>
+      </c>
+      <c r="C82" t="s" s="0">
+        <v>246</v>
+      </c>
+      <c r="D82" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E82" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="F82" t="n" s="0">
+        <v>24.0</v>
+      </c>
+      <c r="G82" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H82" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I82" t="n" s="0">
+        <v>0.16599999368190765</v>
+      </c>
+      <c r="J82" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>247</v>
+      </c>
+      <c r="B83" t="s" s="0">
+        <v>248</v>
+      </c>
+      <c r="C83" t="s" s="0">
+        <v>249</v>
+      </c>
+      <c r="D83" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E83" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F83" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="G83" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H83" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I83" t="n" s="0">
+        <v>0.24500000476837158</v>
+      </c>
+      <c r="J83" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>250</v>
+      </c>
+      <c r="B84" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="C84" t="s" s="0">
+        <v>252</v>
+      </c>
+      <c r="D84" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E84" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F84" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G84" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H84" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I84" t="n" s="0">
+        <v>0.12800000607967377</v>
+      </c>
+      <c r="J84" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="B85" t="s" s="0">
+        <v>254</v>
+      </c>
+      <c r="C85" t="s" s="0">
+        <v>255</v>
+      </c>
+      <c r="D85" t="n" s="0">
+        <v>494.0</v>
+      </c>
+      <c r="E85" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F85" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G85" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H85" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I85" t="n" s="0">
+        <v>221.6330108642578</v>
+      </c>
+      <c r="J85" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>256</v>
+      </c>
+      <c r="B86" t="s" s="0">
+        <v>257</v>
+      </c>
+      <c r="C86" t="s" s="0">
+        <v>258</v>
+      </c>
+      <c r="D86" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E86" t="n" s="0">
+        <v>72.0</v>
+      </c>
+      <c r="F86" t="n" s="0">
+        <v>72.0</v>
+      </c>
+      <c r="G86" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H86" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I86" t="n" s="0">
+        <v>0.23999999463558197</v>
+      </c>
+      <c r="J86" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>259</v>
+      </c>
+      <c r="B87" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="C87" t="s" s="0">
+        <v>261</v>
+      </c>
+      <c r="D87" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="E87" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="F87" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="G87" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H87" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I87" t="n" s="0">
+        <v>0.14499999582767487</v>
+      </c>
+      <c r="J87" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>262</v>
+      </c>
+      <c r="B88" t="s" s="0">
+        <v>263</v>
+      </c>
+      <c r="C88" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="D88" t="n" s="0">
+        <v>191.0</v>
+      </c>
+      <c r="E88" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F88" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G88" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H88" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I88" t="n" s="0">
+        <v>174.32098388671875</v>
+      </c>
+      <c r="J88" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>265</v>
+      </c>
+      <c r="B89" t="s" s="0">
+        <v>266</v>
+      </c>
+      <c r="C89" t="s" s="0">
+        <v>267</v>
+      </c>
+      <c r="D89" t="n" s="0">
+        <v>217.0</v>
+      </c>
+      <c r="E89" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F89" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G89" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H89" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I89" t="n" s="0">
+        <v>115.43799591064453</v>
+      </c>
+      <c r="J89" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>268</v>
+      </c>
+      <c r="B90" t="s" s="0">
+        <v>269</v>
+      </c>
+      <c r="C90" t="s" s="0">
+        <v>270</v>
+      </c>
+      <c r="D90" t="n" s="0">
+        <v>471.0</v>
+      </c>
+      <c r="E90" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F90" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G90" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H90" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I90" t="n" s="0">
+        <v>183.48301696777344</v>
+      </c>
+      <c r="J90" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>271</v>
+      </c>
+      <c r="B91" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="C91" t="s" s="0">
+        <v>272</v>
+      </c>
+      <c r="D91" t="n" s="0">
+        <v>553.0</v>
+      </c>
+      <c r="E91" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F91" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G91" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H91" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I91" t="n" s="0">
+        <v>257.7050476074219</v>
+      </c>
+      <c r="J91" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="0">
+        <v>273</v>
+      </c>
+      <c r="B92" t="s" s="0">
+        <v>274</v>
+      </c>
+      <c r="C92" t="s" s="0">
+        <v>275</v>
+      </c>
+      <c r="D92" t="n" s="0">
+        <v>667.0</v>
+      </c>
+      <c r="E92" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F92" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G92" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H92" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I92" t="n" s="0">
+        <v>334.90704345703125</v>
+      </c>
+      <c r="J92" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="0">
+        <v>276</v>
+      </c>
+      <c r="B93" t="s" s="0">
+        <v>277</v>
+      </c>
+      <c r="C93" t="s" s="0">
+        <v>278</v>
+      </c>
+      <c r="D93" t="n" s="0">
+        <v>43.0</v>
+      </c>
+      <c r="E93" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F93" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="G93" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H93" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I93" t="n" s="0">
+        <v>24.354999542236328</v>
+      </c>
+      <c r="J93" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="0">
+        <v>279</v>
+      </c>
+      <c r="B94" t="s" s="0">
+        <v>280</v>
+      </c>
+      <c r="C94" t="s" s="0">
+        <v>281</v>
+      </c>
+      <c r="D94" t="n" s="0">
+        <v>653.0</v>
+      </c>
+      <c r="E94" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F94" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="G94" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H94" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I94" t="n" s="0">
+        <v>368.78802490234375</v>
+      </c>
+      <c r="J94" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="0">
+        <v>282</v>
+      </c>
+      <c r="B95" t="s" s="0">
+        <v>283</v>
+      </c>
+      <c r="C95" t="s" s="0">
+        <v>284</v>
+      </c>
+      <c r="D95" t="n" s="0">
+        <v>283.0</v>
+      </c>
+      <c r="E95" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="F95" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="G95" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H95" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I95" t="n" s="0">
+        <v>218.761962890625</v>
+      </c>
+      <c r="J95" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
